--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_39_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_39_IN_Piura.xlsx
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>82.28</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>13.88</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>3.84</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>68.5691</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>65.9335</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>96.16</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1965,11 +1965,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>2.6356</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>3.84</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>68.6001</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2267,6 +2267,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2461,6 +2462,7 @@
       <c r="F15" s="17" t="inlineStr"/>
       <c r="G15" s="17" t="inlineStr"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -2505,6 +2507,7 @@
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="132" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
@@ -2757,11 +2760,11 @@
       </c>
       <c r="B13" s="33">
         <f>SUM(B10:B12)</f>
-        <v/>
+        <v>246.75</v>
       </c>
       <c r="C13" s="23">
         <f>SUM(C10:C12)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -2771,19 +2774,19 @@
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17">
         <f>ROUND(AVERAGE(F10:F12),2)</f>
-        <v/>
+        <v>26.26</v>
       </c>
       <c r="G13" s="22">
         <f>ROUND(AVERAGE(G10:G12),4)</f>
-        <v/>
+        <v>0.6835</v>
       </c>
       <c r="H13" s="23">
         <f>ROUND(AVERAGE(H10:H12),2)</f>
-        <v/>
+        <v>92.85</v>
       </c>
       <c r="I13" s="23">
         <f>ROUND(AVERAGE(I10:I12),2)</f>
-        <v/>
+        <v>3.95</v>
       </c>
     </row>
     <row r="14"/>
